--- a/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/financial_evidence_ledger.xlsx
+++ b/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/financial_evidence_ledger.xlsx
@@ -18134,6 +18134,2398 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FE-000197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>PAYROLL_BRUTTO</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>73703.19</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 01-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Summen aus Lohnabrechnung 000 000 73.70319 73.70319 73.70319 73.70319 2.02491 76.28319 73.70319 5.88913 000 000 6.04922 6.85439 95815 1.79356 33383 1.92806 000 000 000 000 6.04922 6.85439 95815 88444 </t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>document month + Summen aus Lohnabrechnung</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_summary</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>FE-000198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>PAYROLL_BRUTTO</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>82167.64</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 02-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Summen aus Lohnabrechnung 000 000 82.16764 82.39514 82.39514 82.16764 2.25869 85.91544 83.12144 7.25155 000 2607 6.75312 7.66275 1.07115 2.04135 36129 1.88460 000 000 000 000 6.75312 7.66275 1.07115 98602 </t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>document month + Summen aus Lohnabrechnung</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_summary</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>FE-000199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>PAYROLL_BRUTTO</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>81895.08</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 03-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Summen aus Lohnabrechnung 000 000 81.89508 81.89508 81.89508 81.89508 2.26054 85.60508 81.89508 6.55653 000 000 6.73660 7.61623 1.06464 2.04315 36589 54060 000 000 000 000 6.73660 7.61623 1.06464 98274 </t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>document month + Summen aus Lohnabrechnung</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_summary</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>FE-000200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>33596.07</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 06-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>AOK Baden-Württemberg 70025 Stuttgart Überweisung 89878877 253,34 AOK Bayern Die Gesundheitsk 81739 München Überweisung 89878877 1.125,65 AOK Hessen 61281 Bad Homburg Überweisung 89878877 1.244,22 AOK Nordost 14456 Potsdam Überweisung 89878877 1.187,06 AOK PLUS 01058 Dresden Überweisung 89878877 8.617,36 AOK Sachsen-Anhalt 39106 Magdeburg Keine Überw. 89878877 1.159,45- BKK Linde 65030 Wiesbaden Keine Überw. 89878877 1.351,67- BKK SBK 80227 München Überweisung 89878877 1.239,23 BKK VIACTIV 44803</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>FE-000201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>PAYROLL_BRUTTO</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>72130.67</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 07-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Summen aus Lohnabrechnung 000 000 72.13067 72.13067 72.13067 72.13067 2.02098 76.75067 72.13067 5.51516 000 000 5.93721 6.70815 93770 1.83285 31584 13878- 000 000 000 000 5.93721 6.70815 93770 86557 </t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>document month + Summen aus Lohnabrechnung</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_summary</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>FE-000202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>33270.79</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 07-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>AOK Baden-Württemberg 70025 Stuttgart Überweisung 89878877 81,11 AOK Bayern Die Gesundheitsk 81739 München Überweisung 89878877 1.125,65 AOK Hessen 61281 Bad Homburg Überweisung 89878877 1.244,22 AOK Nordost 14456 Potsdam Überweisung 89878877 1.187,06 AOK PLUS 01058 Dresden Überweisung 89878877 9.219,88 BKK Linde 65030 Wiesbaden Überweisung 89878877 750,96 BKK SBK 80227 München Überweisung 89878877 1.125,14 BKK VIACTIV 44803 Bochum Überweisung 89878877 1.227,60 EK BARMER 42271 Wuppertal Überweis</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>FE-000203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PAYROLL_BRUTTO</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>84126.70</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/payroll082024/Lohnauswertungen.pdf</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Summen aus Lohnabrechnung 000 000 84.12670 84.58170 84.58170 84.12670 2.27955 87.06105 84.88105 7.00240 000 000 7.17131 7.86609 1.09958 2.14699 34227 74322 000 000 000 000 7.17131 7.86609 1.09958 1.00951 </t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>document month + Summen aus Lohnabrechnung</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_summary</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>FE-000204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>32919.94</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 08-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>AOK Bayern Die Gesundheitsk 81739 München Überweisung 89878877 472,01 AOK Hessen 61281 Bad Homburg Überweisung 89878877 1.244,22 AOK Nordost 14456 Potsdam Keine Überw. 89878877 1.187,06- AOK PLUS 01058 Dresden Bar/Einzug 89878877 8.240,74 BKK Linde 65030 Wiesbaden Überweisung 89878877 1.296,02 BKK SBK 80227 München Überweisung 89878877 1.125,14 BKK VIACTIV 44803 Bochum Überweisung 89878877 1.227,60 EK BARMER 42271 Wuppertal Überweisung 89878877 2.303,42 EK DAK Gesundheit 20009 Hamburg Bar/Einzug</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>FE-000205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>TAX_DUE</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>7002.40</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 08-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>r Lohnsteuer-Anmeldung---------------------- Lohnsteuer 7.00240</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>document month + Lohnsteuer-Anmeldung Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_tax_summary</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>FE-000206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>39302.86</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 09-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>AOK Bayern Die Gesundheitsk 81739 München Keine Überw. 89878877 798,83- AOK Hessen 61281 Bad Homburg Überweisung 89878877 1.244,22 AOK PLUS 01058 Dresden Bar/Einzug 89878877 11.253,52 BKK Linde 65030 Wiesbaden Überweisung 89878877 1.417,11 BKK SBK 80227 München Überweisung 89878877 326,66 BKK VIACTIV 44803 Bochum Überweisung 89878877 1.227,60 BKK vivida 78056 Villingen-Schwe Überweisung 89878877 544,82 EK BARMER 42271 Wuppertal Überweisung 89878877 3.501,30 EK DAK Gesundheit 20009 Hamburg Bar/Ei</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>FE-000207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>PAYROLL_BRUTTO</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>84245.80</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/payroll102024/Lohnauswertungen.pdf</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Summen aus Lohnabrechnung 000 000 84.24580 84.24580 84.24580 84.24580 2.37387 130.42580 84.24580 6.36490 000 000 7.13681 7.83486 1.09520 2.15590 38094 1.56099- 000 000 000 000 7.13681 7.83486 1.09520 1.01096 </t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>document month + Summen aus Lohnabrechnung</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_summary</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>FE-000208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>40678.01</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 10-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>AOK Hessen 61281 Bad Homburg Überweisung 89878877 1.244,22 AOK PLUS 01058 Dresden Bar/Einzug 89878877 15.451,27 BKK Linde 65030 Wiesbaden Überweisung 89878877 1.126,43 BKK SBK 80227 München Überweisung 89878877 1.074,28 BKK VIACTIV 44803 Bochum Überweisung 89878877 1.227,60 EK BARMER 42271 Wuppertal Überweisung 89878877 1.990,52 EK DAK Gesundheit 20009 Hamburg Bar/Einzug 89878877 604,19 EK KKH Kaufmännische Kranke 30144 Hannover Überweisung 89878877 17.870,97 EK Techniker-Krankenkasse 22291 Hamb</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>FE-000209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>40962.45</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 11-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>AOK Hessen 61281 Bad Homburg Überweisung 89878877 1.244,22 AOK PLUS 01058 Dresden Überweisung 89878877 15.042,95 BKK Linde 65030 Wiesbaden Überweisung 89878877 2.378,83 BKK SBK 80227 München Überweisung 89878877 1.350,19 BKK VIACTIV 44803 Bochum Überweisung 89878877 1.227,60 EK BARMER 42271 Wuppertal Überweisung 89878877 1.159,45 EK DAK Gesundheit 20009 Hamburg Fehler 89878877 1.151,97 EK KKH Kaufmännische Kranke 30144 Hannover Überweisung 89878877 15.855,27 EK Techniker-Krankenkasse 22291 Hambu</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>FE-000210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>36525.82</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2024/Entgeltbescheinigungen 12-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>AOK AOK PLUS Die Gesundheit 01058 Dresden Überweisung 89878877 13.913,67 AOK Hessen 61281 Bad Homburg Überweisung 89878877 1.244,22 BKK BKK Linde 65030 Wiesbaden Überweisung 89878877 2.784,05 BKK SBK 80227 München Überweisung 89878877 1.125,14 BKK VIACTIV Krankenkasse 44803 Bochum Überweisung 89878877 1.298,00 EK BARMER 42271 Wuppertal Überweisung 89878877 1.159,45 EK DAK-Gesundheit 20097 Hamburg Überweisung 89878877 1.151,97 EK KKH Kaufmännische Kranke 30625 Hannover Überweisung 89878877 12.737</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>FE-000211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>40514.11</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>AOK AOK Hessen Direktion 61281 Bad Homburg Überweisung 89878877 1.244,22 AOK AOK PLUS Die Gesundheit 01058 Dresden Überweisung 89878877 17.743,16 BKK BKK Linde 65030 Wiesbaden Überweisung 89878877 2.268,34 BKK SBK HV West 80227 München Überweisung 89878877 1.125,14 BKK VIACTIV Krankenkasse 44803 Bochum Überweisung 89878877 1.262,80 EK BARMER (vormals BARMER G 42271 Wuppertal Überweisung 89878877 1.159,45 EK DAK-Gesundheit 20097 Hamburg Überweisung 89878877 1.151,97 EK KKH Kaufmännische Kranke 30</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>FE-000212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>28247.43</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>AOK AOK Hessen Direktion 61281 Bad Homburg Überweisung 89878877 1.158,76 AOK AOK PLUS Die Gesundheit 01058 Dresden Überweisung 89878877 13.812,22 BKK BKK Linde 65030 Wiesbaden Überweisung 89878877 2.164,10 BKK SBK HV West 80227 München Keine Überw. 89878877 311,03- BKK VIACTIV Krankenkasse 44803 Bochum Überweisung 89878877 1.146,76 EK BARMER (vormals BARMER G 42271 Wuppertal Überweisung 89878877 1.099,59 EK DAK-Gesundheit 20097 Hamburg Überweisung 89878877 1.079,21 EK KKH Kaufmännische Kranke 30</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>FE-000213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>TAX_DUE</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>4789.23</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 03-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>r Lohnsteuer-Anmeldung---------------------- Lohnsteuer 4.78923</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>document month + Lohnsteuer-Anmeldung Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_tax_summary</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>FE-000214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>PAYROLL_BRUTTO</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>65981.53</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Summen aus Lohnabrechnung 000 000 65.98153 65.98153 65.98153 65.98153 000 65.98153 65.98153 4.51802 000 000 5.90495 6.13629 85777 1.69994 25781 49366 000 000 000 000 5.90495 6.13629 85777 85777 </t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>document month + Summen aus Lohnabrechnung</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_summary</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>FE-000215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>28906.24</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>AOK Hessen 61281 Bad Homburg Keine Überw. 89878877 348,81- AOK PLUS 01058 Dresden Überweisung 89878877 9.962,60 BKK Linde 65030 Wiesbaden Überweisung 89878877 2.044,44 BKK VIACTIV Krankenkasse 44803 Bochum Überweisung 89878877 1.204,78 EK BARMER 42271 Wuppertal Überweisung 89878877 1.129,52 EK DAK-Gesundheit 20097 Hamburg Überweisung 89878877 1.115,59 EK Kaufmännische Krankenkas 30625 Hannover Überweisung 89878877 12.703,16 EK Techniker Krankenkasse 22305 Hamburg Überweisung 89878877 1.094,96 Fä</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>FE-000216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>TAX_DUE</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>4518.02</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>r Lohnsteuer-Anmeldung---------------------- Lohnsteuer 4.51802</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>document month + Lohnsteuer-Anmeldung Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_tax_summary</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>FE-000217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PAYROLL_BRUTTO</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>51565.19</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 05-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Summen aus Lohnabrechnung 000 000 51.56519 51.56519 51.56519 51.56519 5327 51.56519 51.56519 4.63482 000 000 4.55706 4.79556 67036 1.32526 22372 1856- 000 000 000 000 4.55706 4.79556 67036 67036 </t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>document month + Summen aus Lohnabrechnung</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_summary</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>FE-000218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>27082.96</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 05-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>AOK PLUS 01058 Dresden Überweisung 89878877 9.606,05 BKK Linde 65030 Wiesbaden Überweisung 89878877 2.271,15 BKK VIACTIV Krankenkasse 44803 Bochum Überweisung 89878877 1.204,78 EK BARMER 42271 Wuppertal Überweisung 89878877 1.129,52 EK DAK-Gesundheit 20097 Hamburg Überweisung 89878877 1.413,92 EK Kaufmännische Krankenkas 30625 Hannover Überweisung 89878877 10.362,58 EK Techniker Krankenkasse 22305 Hamburg Überweisung 89878877 1.094,96 Fälligkeit bis: 27.05.2025 (1) 27.082,96 * G e s a m t s u m </t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>FE-000219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>TAX_DUE</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>4634.82</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 05-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>r Lohnsteuer-Anmeldung---------------------- Lohnsteuer 4.63482</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>document month + Lohnsteuer-Anmeldung Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_tax_summary</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>FE-000220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>PAYROLL_BRUTTO</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>34088.77</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Summen aus Lohnabrechnung 000 000 34.08877 34.08877 34.08877 34.08877 000 36.27185 36.27185 2.47401 000 000 3.05939 3.17026 44316 79302 12798 35289- 000 000 000 000 3.05939 3.17026 44316 44316 </t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>document month + Summen aus Lohnabrechnung</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_summary</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>FE-000221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>HEALTH_INSURANCE_DUE</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>10334.33</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>AOK NordWest 58079 Hagen Überweisung 89878877 4.799,13 AOK PLUS 01058 Dresden Überweisung 89878877 889,73 BKK Linde 65030 Wiesbaden Überweisung 89878877 2.200,74 BKK VIACTIV Krankenkasse 44803 Bochum Überweisung 89878877 1.127,04 EK BARMER 42271 Wuppertal Überweisung 89878877 1.129,52 EK DAK-Gesundheit 20097 Hamburg Keine Überw. 89878877 1.007,61- EK Kaufmännische Krankenkas 30625 Hannover Überweisung 89878877 383,40 EK Techniker Krankenkasse 22305 Hamburg Überweisung 89878877 812,38 Fälligkeit </t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>document month + Krankenkasse Gesamtsumme/F?lligkeit</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_health_summary</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>FE-000222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>TAX_DUE</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2474.01</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/2025/Entgeltbescheinigungen 06-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>r Lohnsteuer-Anmeldung---------------------- Lohnsteuer 2.47401</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>document month + Lohnsteuer-Anmeldung Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>gap_candidate_payroll_tax_summary</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/financial_evidence_ledger.xlsx
+++ b/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/financial_evidence_ledger.xlsx
@@ -20526,6 +20526,6170 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>FE-000223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/8. Überweisungsnachweise bzw. Barzahlungsquittungen/# 2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>FE-000224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/audit2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>FE-000225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>FE-000226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy2</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>FE-000227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy3</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy3.pdf</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>FE-000228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/8. Überweisungsnachweise bzw. Barzahlungsquittungen/# 2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>FE-000229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/audit2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>FE-000230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>FE-000231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy2</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>FE-000232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy3</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy3.pdf</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>FE-000233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/8. Überweisungsnachweise bzw. Barzahlungsquittungen/# 2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>FE-000234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/audit2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>FE-000235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>FE-000236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy2</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>FE-000237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy3</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy3.pdf</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>FE-000238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/8. Überweisungsnachweise bzw. Barzahlungsquittungen/# 2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>FE-000239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/audit2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>FE-000240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>FE-000241</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy2</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>FE-000242</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy3</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024__copy3.pdf</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>FE-000243</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/8. Überweisungsnachweise bzw. Barzahlungsquittungen/# 2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>FE-000244</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/audit2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t> Kanzlei-Rechnungswesen V.12.48 08.05.2024 6 Bu.Tag Text Wert Währung Umsatz UEBERWEISUNG 09.01.2024 EUR -4.000,00 09.01.2024 EREF+NOTPROVIDED KREF+3cf78622c7d44eaf84423e ddf8f26b3c SVWZ+transfer Martin Zahariev; BIC: PBNKDEFFXXX; IBAN: DE43 1001 0010 0783 0891 20 KARTENZAHLUNG 09.01.2024 EUR -316,52 09.01.2024 EREF+66078820014974080124133934 MREF+119960 CRED+DE07ZZZ00000843064 SVWZ+Stahlgruber GmbH//Chemnitz/DE 08-01-2024T13:39:34 Folgenr. 01 Verfalld. 1227 STAHLGRUBER GMBH CHEMNITZ; BIC: COBAD</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>FE-000245</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>20.23</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/8. Überweisungsnachweise bzw. Barzahlungsquittungen/# 2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>3 Tagessumme: EUR Auszug/Blatt: 125/1 04.07.2023 Neuer Kontostand: EUR 1.983,38 UEBERWEISUNG 05.07.2023 EUR -200,00 05.07.2023 EREF+NOTPROVIDED KREF+4ef885d5607348f19b69fc 6d7021aa84 SVWZ+S-2927/DE8572170024023 5291200 Vorschuss Gehalt 06/2023 Stanislav Sokolarski; BIC: DEUTDEDB721; IBAN: DE85 7217 0024 0235 2912 00 UEBERWEISUNG 05.07.2023 EUR -100,00 05.07.2023 EREF+NOTPROVIDED KREF+00d023babe544af0b05547 da5099c78f SVWZ+Transfer Petya Stefanova; BIC: PBNKDEFFXXX; IBAN: DE31 1001 0010 0901 1351</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>FE-000246</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>20.23</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/audit2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>3 Tagessumme: EUR Auszug/Blatt: 125/1 04.07.2023 Neuer Kontostand: EUR 1.983,38 UEBERWEISUNG 05.07.2023 EUR -200,00 05.07.2023 EREF+NOTPROVIDED KREF+4ef885d5607348f19b69fc 6d7021aa84 SVWZ+S-2927/DE8572170024023 5291200 Vorschuss Gehalt 06/2023 Stanislav Sokolarski; BIC: DEUTDEDB721; IBAN: DE85 7217 0024 0235 2912 00 UEBERWEISUNG 05.07.2023 EUR -100,00 05.07.2023 EREF+NOTPROVIDED KREF+00d023babe544af0b05547 da5099c78f SVWZ+Transfer Petya Stefanova; BIC: PBNKDEFFXXX; IBAN: DE31 1001 0010 0901 1351</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>FE-000247</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>20.23</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/8. Überweisungsnachweise bzw. Barzahlungsquittungen/# 2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>3 Tagessumme: EUR Auszug/Blatt: 125/1 04.07.2023 Neuer Kontostand: EUR 1.983,38 UEBERWEISUNG 05.07.2023 EUR -200,00 05.07.2023 EREF+NOTPROVIDED KREF+4ef885d5607348f19b69fc 6d7021aa84 SVWZ+S-2927/DE8572170024023 5291200 Vorschuss Gehalt 06/2023 Stanislav Sokolarski; BIC: DEUTDEDB721; IBAN: DE85 7217 0024 0235 2912 00 UEBERWEISUNG 05.07.2023 EUR -100,00 05.07.2023 EREF+NOTPROVIDED KREF+00d023babe544af0b05547 da5099c78f SVWZ+Transfer Petya Stefanova; BIC: PBNKDEFFXXX; IBAN: DE31 1001 0010 0901 1351</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>FE-000248</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>20.23</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/8. Überweisungsnachweise bzw. Barzahlungsquittungen/# 2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>3 Tagessumme: EUR Auszug/Blatt: 125/1 04.07.2023 Neuer Kontostand: EUR 1.983,38 UEBERWEISUNG 05.07.2023 EUR -200,00 05.07.2023 EREF+NOTPROVIDED KREF+4ef885d5607348f19b69fc 6d7021aa84 SVWZ+S-2927/DE8572170024023 5291200 Vorschuss Gehalt 06/2023 Stanislav Sokolarski; BIC: DEUTDEDB721; IBAN: DE85 7217 0024 0235 2912 00 UEBERWEISUNG 05.07.2023 EUR -100,00 05.07.2023 EREF+NOTPROVIDED KREF+00d023babe544af0b05547 da5099c78f SVWZ+Transfer Petya Stefanova; BIC: PBNKDEFFXXX; IBAN: DE31 1001 0010 0901 1351</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>FE-000249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>20.23</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting/audit2024/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>3 Tagessumme: EUR Auszug/Blatt: 125/1 04.07.2023 Neuer Kontostand: EUR 1.983,38 UEBERWEISUNG 05.07.2023 EUR -200,00 05.07.2023 EREF+NOTPROVIDED KREF+4ef885d5607348f19b69fc 6d7021aa84 SVWZ+S-2927/DE8572170024023 5291200 Vorschuss Gehalt 06/2023 Stanislav Sokolarski; BIC: DEUTDEDB721; IBAN: DE85 7217 0024 0235 2912 00 UEBERWEISUNG 05.07.2023 EUR -100,00 05.07.2023 EREF+NOTPROVIDED KREF+00d023babe544af0b05547 da5099c78f SVWZ+Transfer Petya Stefanova; BIC: PBNKDEFFXXX; IBAN: DE31 1001 0010 0901 1351</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>ueberweisung</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>FE-000250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>UNKNOWN_AMOUNT_DO_NOT_SUM</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>3.0.2_920_v6.2_20240101_gebuehrenordnung_pq_kep</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/3.0.2_920_v6.2_20240101_gebuehrenordnung_pq_kep.pdf</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t> Gebührenordnung PQ KEP (Stand 01/01/2024) 3.0.2_920_v6.2_ 20240101 Zertifizierung Bau GmbH • Kronenstraße 55 – 58 • 10117 Berlin Seite 1</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>amount without strict status label</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>Operating invoice/amount found, but due/paid/unpaid meaning is unclear; not summed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>FE-000251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t> Umsatzsteuerbeträge gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>FE-000252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t> Umsatzsteuerbeträge gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>FE-000253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Die Pauschale für die Lohnabrechnung pro Arbeitnehmer wurde zum 01.01.2024 von 15,-€ auf 17,- € erhöht. Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>FE-000254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Die Pauschale für die Lohnabrechnung pro Arbeitnehmer wurde zum 01.01.2024 von 15,-€ auf 17,- € erhöht. Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>FE-000255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>FE-000256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>FE-000257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>18516.48</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>41467 - Accountings 02-2024</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41467 - Accountings 02-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 8.729,53 37 Verbleibender Betrag 18.516,48 44 USt-Vorauszahlung / Überschuss 18.516,48 47 Umsatzsteuer - Vorauszahlung 83 18.516,48 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FAW </t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>FE-000258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>FE-000259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>FE-000260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>FE-000261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>FE-000262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>FE-000263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1__copy2</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>FE-000264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>FE-000265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303__co</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>FE-000266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>FE-000267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>FE-000268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>FE-000269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>FE-000270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>FE-000271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>FE-000272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Man</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>FE-000273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Man</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>FE-000274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t> Umsatzsteuerbeträge gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>FE-000275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t> Umsatzsteuerbeträge gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>FE-000276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>FE-000277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_UNPAID</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303__copy2</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00 % gemäß § 15 StBVV Rechnungsbetrag Bitte überweisen Sie den offenen Rechnungsbetrag unter Angabe der Rechnungsnummer auf das oben genannte Konto. 20,00 EUR Summe Post- und Telekommunikationsdienstleistungen Mit freundlichen Grüßen Seite 2 </t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>FE-000278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>20797.47</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Accountings 01-2024</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 01-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 4.899,75 37 Verbleibender Betrag 20.797,47 44 USt-Vorauszahlung / Überschuss 20.797,47 47 Umsatzsteuer - Vorauszahlung 83 20.797,47 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FAJ </t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>FE-000279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>24159.32</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Accountings 01-2025</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 6.195,91 38 Verbleibender Betrag 24.159,32 45 USt-Vorauszahlung / Überschuss 24.159,32 48 Umsatzsteuer - Vorauszahlung 83 24.159,32 50 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2025*FAH </t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>FE-000280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>22523.36</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Accountings 02-2025</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 4.749,14 38 Verbleibender Betrag 22.523,36 45 USt-Vorauszahlung / Überschuss 22.523,36 48 Umsatzsteuer - Vorauszahlung 83 22.523,36 50 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2025*FAL </t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>FE-000281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>22853.99</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Accountings 04-2024</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 04-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 6.305,85 37 Verbleibender Betrag 22.853,99 44 USt-Vorauszahlung / Überschuss 22.853,99 47 Umsatzsteuer - Vorauszahlung 83 22.853,99 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FA6 </t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>FE-000282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>24018.01</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Accountings 05-2024</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 05-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 5.544,94 37 Verbleibender Betrag 24.018,01 44 USt-Vorauszahlung / Überschuss 24.018,01 47 Umsatzsteuer - Vorauszahlung 83 24.018,01 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FBE </t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>FE-000283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>23553.36</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Accountings 06-2024</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 06-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 6.140,68 37 Verbleibender Betrag 23.553,36 44 USt-Vorauszahlung / Überschuss 23.553,36 47 Umsatzsteuer - Vorauszahlung 83 23.553,36 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FBH </t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>FE-000284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>23067.09</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Accountings 07-2024</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 07-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 5.733,50 37 Verbleibender Betrag 23.067,09 44 USt-Vorauszahlung / Überschuss 23.067,09 47 Umsatzsteuer - Vorauszahlung 83 23.067,09 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FBL </t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>FE-000285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>22536.76</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Accountings 09-2024</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 09-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 5.687,82 37 Verbleibender Betrag 22.536,76 44 USt-Vorauszahlung / Überschuss 22.536,76 47 Umsatzsteuer - Vorauszahlung 83 22.536,76 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FBV </t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>FE-000286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>24226.58</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Accountings 10-2024</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 10-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 7.384,11 37 Verbleibender Betrag 24.226,58 44 USt-Vorauszahlung / Überschuss 24.226,58 47 Umsatzsteuer - Vorauszahlung 83 24.226,58 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FBY </t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>FE-000287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>27948.98</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Accountings 11-2024</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 11-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 9.230,26 37 Verbleibender Betrag 27.948,98 44 USt-Vorauszahlung / Überschuss 27.948,98 47 Umsatzsteuer - Vorauszahlung 83 27.948,98 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FB6 </t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>FE-000288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>OPERATING_COST_PAID</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>23984.73</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Accountings 12-2024</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Accountings 12-2024.pdf</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>are Vorsteuerbeträge 66 6.268,71 37 Verbleibender Betrag 23.984,73 44 USt-Vorauszahlung / Überschuss 23.984,73 47 Abzug der festgesetzten Sondervorauszahlung 39 25.186,00 48 Umsatzsteuer - Überschuss 83 -1.201,27 49 Die Auswertung entspricht dem derzeitigen Stand der Buchführung. Währung: EUR Status 2024*FB6 </t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>zahlung</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>FE-000289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Operating Cost</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>UNKNOWN_AMOUNT_DO_NOT_SUM</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>BWA 03-2025</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/BWA 03-2025.pdf</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Bezeichnung Mrz/2025 % Ges.- Leistg. % Ges.- Kosten % Pers.- Kosten Auf- schlag Jan/2025 - Mrz/2025 % Ges.- Leistg. % Ges.- Kost</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>amount without strict status label</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>operating_cost_gap_resolver</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>Operating invoice/amount found, but due/paid/unpaid meaning is unclear; not summed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>